--- a/04_Figures/F04_association/modules/training/lm/c_data/results.xlsx
+++ b/04_Figures/F04_association/modules/training/lm/c_data/results.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
   <si>
     <t xml:space="preserve">outcome</t>
   </si>
@@ -69,12 +69,6 @@
   </si>
   <si>
     <t xml:space="preserve">ME_red</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_salmon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_tan</t>
   </si>
   <si>
     <t xml:space="preserve">ME_turquoise</t>
@@ -488,16 +482,16 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.860636703010369</v>
+        <v>10.283008900519</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.0740251530779847</v>
+        <v>0.552371929481484</v>
       </c>
       <c r="F2" t="n">
-        <v>0.942210025788393</v>
+        <v>0.590833754519684</v>
       </c>
       <c r="G2" t="n">
-        <v>0.942210025788393</v>
+        <v>0.942858275045237</v>
       </c>
     </row>
     <row r="3">
@@ -511,16 +505,16 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>12.7006864838535</v>
+        <v>-5.83094949889251</v>
       </c>
       <c r="E3" t="n">
-        <v>0.851946835218943</v>
+        <v>-0.305304183989028</v>
       </c>
       <c r="F3" t="n">
-        <v>0.410923952760863</v>
+        <v>0.765365404005867</v>
       </c>
       <c r="G3" t="n">
-        <v>0.942210025788393</v>
+        <v>0.942858275045237</v>
       </c>
     </row>
     <row r="4">
@@ -534,16 +528,16 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>5.55740719344769</v>
+        <v>6.97664913047096</v>
       </c>
       <c r="E4" t="n">
-        <v>0.45773471978705</v>
+        <v>0.598035852035276</v>
       </c>
       <c r="F4" t="n">
-        <v>0.655320390171873</v>
+        <v>0.560933601130602</v>
       </c>
       <c r="G4" t="n">
-        <v>0.942210025788393</v>
+        <v>0.942858275045237</v>
       </c>
     </row>
     <row r="5">
@@ -557,16 +551,16 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>-3.62582831597112</v>
+        <v>-5.44004819871796</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.157345643037983</v>
+        <v>-0.444245026785018</v>
       </c>
       <c r="F5" t="n">
-        <v>0.877588934820565</v>
+        <v>0.664770928741711</v>
       </c>
       <c r="G5" t="n">
-        <v>0.942210025788393</v>
+        <v>0.942858275045237</v>
       </c>
     </row>
     <row r="6">
@@ -580,16 +574,16 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>20.326751432546</v>
+        <v>22.2331749845204</v>
       </c>
       <c r="E6" t="n">
-        <v>1.23182813213486</v>
+        <v>1.36617201078</v>
       </c>
       <c r="F6" t="n">
-        <v>0.241606621485178</v>
+        <v>0.196940819834865</v>
       </c>
       <c r="G6" t="n">
-        <v>0.942210025788393</v>
+        <v>0.942858275045237</v>
       </c>
     </row>
     <row r="7">
@@ -603,16 +597,16 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>-6.09287076742309</v>
+        <v>-0.861819092579613</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.655300145980683</v>
+        <v>-0.0731931714705972</v>
       </c>
       <c r="F7" t="n">
-        <v>0.524638292178718</v>
+        <v>0.942858275045237</v>
       </c>
       <c r="G7" t="n">
-        <v>0.942210025788393</v>
+        <v>0.942858275045237</v>
       </c>
     </row>
     <row r="8">
@@ -626,16 +620,16 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>13.130847241387</v>
+        <v>2.25661551231133</v>
       </c>
       <c r="E8" t="n">
-        <v>0.84910500865881</v>
+        <v>0.120340385319095</v>
       </c>
       <c r="F8" t="n">
-        <v>0.412441907674149</v>
+        <v>0.906204919558332</v>
       </c>
       <c r="G8" t="n">
-        <v>0.942210025788393</v>
+        <v>0.942858275045237</v>
       </c>
     </row>
     <row r="9">
@@ -649,16 +643,16 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>2.3493767514162</v>
+        <v>6.88052716552857</v>
       </c>
       <c r="E9" t="n">
-        <v>0.124647097822488</v>
+        <v>0.519987333548832</v>
       </c>
       <c r="F9" t="n">
-        <v>0.902866655982491</v>
+        <v>0.61253056350931</v>
       </c>
       <c r="G9" t="n">
-        <v>0.942210025788393</v>
+        <v>0.942858275045237</v>
       </c>
     </row>
     <row r="10">
@@ -672,16 +666,16 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.62351749580375</v>
+        <v>0.963637377326914</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.373326460675884</v>
+        <v>0.0744575155016268</v>
       </c>
       <c r="F10" t="n">
-        <v>0.71541704454443</v>
+        <v>0.941873162039769</v>
       </c>
       <c r="G10" t="n">
-        <v>0.942210025788393</v>
+        <v>0.942858275045237</v>
       </c>
     </row>
     <row r="11">
@@ -695,16 +689,16 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.50708807484155</v>
+        <v>-3.95217342991792</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.16300983263656</v>
+        <v>-0.356489175204703</v>
       </c>
       <c r="F11" t="n">
-        <v>0.87322366935084</v>
+        <v>0.727663721167176</v>
       </c>
       <c r="G11" t="n">
-        <v>0.942210025788393</v>
+        <v>0.942858275045237</v>
       </c>
     </row>
     <row r="12">
@@ -718,62 +712,16 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>-25.1350964162605</v>
+        <v>3.60640746322728</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.63650859900854</v>
+        <v>0.292651593001735</v>
       </c>
       <c r="F12" t="n">
-        <v>0.127671971343964</v>
+        <v>0.77478710770032</v>
       </c>
       <c r="G12" t="n">
-        <v>0.942210025788393</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>7</v>
-      </c>
-      <c r="B13" t="n">
-        <v>14</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" t="n">
-        <v>-3.66041828282599</v>
-      </c>
-      <c r="E13" t="n">
-        <v>-0.330198182262591</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.746943494691116</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.942210025788393</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>7</v>
-      </c>
-      <c r="B14" t="n">
-        <v>14</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" t="n">
-        <v>2.28015046160159</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0.170262124844753</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.867640865413596</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.942210025788393</v>
+        <v>0.942858275045237</v>
       </c>
     </row>
   </sheetData>
@@ -812,7 +760,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B2" t="n">
         <v>14</v>
@@ -821,21 +769,21 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>511.385179233931</v>
+        <v>1773.36856156609</v>
       </c>
       <c r="E2" t="n">
-        <v>0.258801302466309</v>
+        <v>0.559235003909121</v>
       </c>
       <c r="F2" t="n">
-        <v>0.800174429831621</v>
+        <v>0.586287331951325</v>
       </c>
       <c r="G2" t="n">
-        <v>0.951355903335092</v>
+        <v>0.92544134677293</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B3" t="n">
         <v>14</v>
@@ -844,21 +792,21 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>2758.19340382393</v>
+        <v>-4328.67797977833</v>
       </c>
       <c r="E3" t="n">
-        <v>1.10692751298561</v>
+        <v>-1.43405621804673</v>
       </c>
       <c r="F3" t="n">
-        <v>0.290021323443945</v>
+        <v>0.177097444813889</v>
       </c>
       <c r="G3" t="n">
-        <v>0.628379534128547</v>
+        <v>0.92544134677293</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B4" t="n">
         <v>14</v>
@@ -867,21 +815,21 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>2206.64046932079</v>
+        <v>1742.53854957466</v>
       </c>
       <c r="E4" t="n">
-        <v>1.11046421916166</v>
+        <v>0.892023583652356</v>
       </c>
       <c r="F4" t="n">
-        <v>0.288555066311621</v>
+        <v>0.389917077831118</v>
       </c>
       <c r="G4" t="n">
-        <v>0.628379534128547</v>
+        <v>0.92544134677293</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B5" t="n">
         <v>14</v>
@@ -890,21 +838,21 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>-4656.09163271045</v>
+        <v>351.473081673162</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.26059489230422</v>
+        <v>0.167272599285412</v>
       </c>
       <c r="F5" t="n">
-        <v>0.231415013993378</v>
+        <v>0.869941313311756</v>
       </c>
       <c r="G5" t="n">
-        <v>0.628379534128547</v>
+        <v>0.92544134677293</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B6" t="n">
         <v>14</v>
@@ -913,21 +861,21 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>3353.70333230988</v>
+        <v>3721.83016523187</v>
       </c>
       <c r="E6" t="n">
-        <v>1.18808948618608</v>
+        <v>1.33855744794223</v>
       </c>
       <c r="F6" t="n">
-        <v>0.257781291559431</v>
+        <v>0.205523323768261</v>
       </c>
       <c r="G6" t="n">
-        <v>0.628379534128547</v>
+        <v>0.92544134677293</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B7" t="n">
         <v>14</v>
@@ -936,21 +884,21 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>-762.676513143546</v>
+        <v>479.155867455339</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.477485530605402</v>
+        <v>0.239341406141313</v>
       </c>
       <c r="F7" t="n">
-        <v>0.641595556583391</v>
+        <v>0.814879946704451</v>
       </c>
       <c r="G7" t="n">
-        <v>0.926749137287121</v>
+        <v>0.92544134677293</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B8" t="n">
         <v>14</v>
@@ -959,21 +907,21 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>1494.46784401706</v>
+        <v>-363.388333854032</v>
       </c>
       <c r="E8" t="n">
-        <v>0.557951504510054</v>
+        <v>-0.113722442037293</v>
       </c>
       <c r="F8" t="n">
-        <v>0.587136188674914</v>
+        <v>0.911338314906148</v>
       </c>
       <c r="G8" t="n">
-        <v>0.926749137287121</v>
+        <v>0.92544134677293</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B9" t="n">
         <v>14</v>
@@ -982,21 +930,21 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>105.579057828425</v>
+        <v>236.250413465526</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0328545268278214</v>
+        <v>0.10366899332158</v>
       </c>
       <c r="F9" t="n">
-        <v>0.974330747023785</v>
+        <v>0.9191444810913</v>
       </c>
       <c r="G9" t="n">
-        <v>0.974330747023785</v>
+        <v>0.92544134677293</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B10" t="n">
         <v>14</v>
@@ -1005,21 +953,21 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>349.550473197521</v>
+        <v>210.718062609346</v>
       </c>
       <c r="E10" t="n">
-        <v>0.164876739389465</v>
+        <v>0.0955676582771065</v>
       </c>
       <c r="F10" t="n">
-        <v>0.871785832662767</v>
+        <v>0.92544134677293</v>
       </c>
       <c r="G10" t="n">
-        <v>0.951355903335092</v>
+        <v>0.92544134677293</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B11" t="n">
         <v>14</v>
@@ -1028,21 +976,21 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>-1667.81479753057</v>
+        <v>-1019.06929145149</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.11054362041339</v>
+        <v>-0.54318834680297</v>
       </c>
       <c r="F11" t="n">
-        <v>0.288522212757765</v>
+        <v>0.596945906740238</v>
       </c>
       <c r="G11" t="n">
-        <v>0.628379534128547</v>
+        <v>0.92544134677293</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B12" t="n">
         <v>14</v>
@@ -1051,62 +999,16 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>-5568.23814542875</v>
+        <v>1820.20353374033</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.31332967118602</v>
+        <v>0.891949765820091</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0392387625178995</v>
+        <v>0.389955082670293</v>
       </c>
       <c r="G12" t="n">
-        <v>0.510103912732693</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>21</v>
-      </c>
-      <c r="B13" t="n">
-        <v>14</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" t="n">
-        <v>-958.77354052212</v>
-      </c>
-      <c r="E13" t="n">
-        <v>-0.510758250317407</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.618786018783704</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.926749137287121</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>21</v>
-      </c>
-      <c r="B14" t="n">
-        <v>14</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" t="n">
-        <v>-357.379629047486</v>
-      </c>
-      <c r="E14" t="n">
-        <v>-0.156586023503851</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.878174680001623</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.951355903335092</v>
+        <v>0.92544134677293</v>
       </c>
     </row>
   </sheetData>
@@ -1145,7 +1047,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B2" t="n">
         <v>14</v>
@@ -1154,21 +1056,21 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>-16.8653148271828</v>
+        <v>1578.25647329676</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.00914698763121096</v>
+        <v>0.53427326437697</v>
       </c>
       <c r="F2" t="n">
-        <v>0.992852170617285</v>
+        <v>0.602910280574815</v>
       </c>
       <c r="G2" t="n">
-        <v>0.992852170617285</v>
+        <v>0.983933293833422</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B3" t="n">
         <v>14</v>
@@ -1177,21 +1079,21 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>2400.02306748306</v>
+        <v>-4935.23999443417</v>
       </c>
       <c r="E3" t="n">
-        <v>1.02852747880304</v>
+        <v>-1.83778644245267</v>
       </c>
       <c r="F3" t="n">
-        <v>0.32398785743652</v>
+        <v>0.0909663304445072</v>
       </c>
       <c r="G3" t="n">
-        <v>0.70197369111246</v>
+        <v>0.675838230023344</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B4" t="n">
         <v>14</v>
@@ -1200,21 +1102,21 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>2373.82871666731</v>
+        <v>1476.36946794161</v>
       </c>
       <c r="E4" t="n">
-        <v>1.30658381152674</v>
+        <v>0.807632022768297</v>
       </c>
       <c r="F4" t="n">
-        <v>0.21584111641428</v>
+        <v>0.435019944544362</v>
       </c>
       <c r="G4" t="n">
-        <v>0.568942892422228</v>
+        <v>0.983933293833422</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B5" t="n">
         <v>14</v>
@@ -1223,21 +1125,21 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>-5766.10953458761</v>
+        <v>765.845390507639</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.77052348877521</v>
+        <v>0.393756929225496</v>
       </c>
       <c r="F5" t="n">
-        <v>0.102015646315148</v>
+        <v>0.700667468758801</v>
       </c>
       <c r="G5" t="n">
-        <v>0.568942892422228</v>
+        <v>0.983933293833422</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B6" t="n">
         <v>14</v>
@@ -1246,21 +1148,21 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>3825.78076618604</v>
+        <v>4151.47838374469</v>
       </c>
       <c r="E6" t="n">
-        <v>1.50161554111075</v>
+        <v>1.65960793724588</v>
       </c>
       <c r="F6" t="n">
-        <v>0.15904481530892</v>
+        <v>0.122879678186063</v>
       </c>
       <c r="G6" t="n">
-        <v>0.568942892422228</v>
+        <v>0.675838230023344</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B7" t="n">
         <v>14</v>
@@ -1269,21 +1171,21 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>-766.789850506871</v>
+        <v>-38.3946188965893</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.51672603994616</v>
+        <v>-0.0205616212748506</v>
       </c>
       <c r="F7" t="n">
-        <v>0.614737457192419</v>
+        <v>0.983933293833422</v>
       </c>
       <c r="G7" t="n">
-        <v>0.837835071554129</v>
+        <v>0.983933293833422</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B8" t="n">
         <v>14</v>
@@ -1292,21 +1194,21 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>1388.78967438055</v>
+        <v>344.913250988605</v>
       </c>
       <c r="E8" t="n">
-        <v>0.557190670417954</v>
+        <v>0.116002403492959</v>
       </c>
       <c r="F8" t="n">
-        <v>0.587639678038983</v>
+        <v>0.909569313782624</v>
       </c>
       <c r="G8" t="n">
-        <v>0.837835071554129</v>
+        <v>0.983933293833422</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B9" t="n">
         <v>14</v>
@@ -1315,21 +1217,21 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>875.17422991564</v>
+        <v>-198.161383760597</v>
       </c>
       <c r="E9" t="n">
-        <v>0.293711075020743</v>
+        <v>-0.0934396748107189</v>
       </c>
       <c r="F9" t="n">
-        <v>0.773996705894278</v>
+        <v>0.927096242554366</v>
       </c>
       <c r="G9" t="n">
-        <v>0.838496431385468</v>
+        <v>0.983933293833422</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B10" t="n">
         <v>14</v>
@@ -1338,21 +1240,21 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>750.452765071275</v>
+        <v>-84.6561735588149</v>
       </c>
       <c r="E10" t="n">
-        <v>0.38228075444094</v>
+        <v>-0.0412482793887495</v>
       </c>
       <c r="F10" t="n">
-        <v>0.708937368238109</v>
+        <v>0.967776323421701</v>
       </c>
       <c r="G10" t="n">
-        <v>0.837835071554129</v>
+        <v>0.983933293833422</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B11" t="n">
         <v>14</v>
@@ -1361,21 +1263,21 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>-1783.21502087655</v>
+        <v>-815.492404145446</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.29757185676518</v>
+        <v>-0.465642946133188</v>
       </c>
       <c r="F11" t="n">
-        <v>0.218824189393164</v>
+        <v>0.649808793428134</v>
       </c>
       <c r="G11" t="n">
-        <v>0.568942892422228</v>
+        <v>0.983933293833422</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B12" t="n">
         <v>14</v>
@@ -1384,62 +1286,16 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>-4883.18407303426</v>
+        <v>2005.75531081425</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.12780025231118</v>
+        <v>1.070636634538</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0547690666646102</v>
+        <v>0.305394724955687</v>
       </c>
       <c r="G12" t="n">
-        <v>0.568942892422228</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>22</v>
-      </c>
-      <c r="B13" t="n">
-        <v>14</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" t="n">
-        <v>-757.650383691345</v>
-      </c>
-      <c r="E13" t="n">
-        <v>-0.432442580831606</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.673089138593961</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.837835071554129</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>22</v>
-      </c>
-      <c r="B14" t="n">
-        <v>14</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" t="n">
-        <v>-836.51990280888</v>
-      </c>
-      <c r="E14" t="n">
-        <v>-0.396048776848478</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.699020676095892</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.837835071554129</v>
+        <v>0.983933293833422</v>
       </c>
     </row>
   </sheetData>
@@ -1478,7 +1334,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B2" t="n">
         <v>14</v>
@@ -1487,21 +1343,21 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.470245848408708</v>
+        <v>1.44348257032395</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.194294981988483</v>
+        <v>0.369420139158803</v>
       </c>
       <c r="F2" t="n">
-        <v>0.849195299928082</v>
+        <v>0.718251118385634</v>
       </c>
       <c r="G2" t="n">
-        <v>0.976206479905453</v>
+        <v>0.920367854693366</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B3" t="n">
         <v>14</v>
@@ -1510,21 +1366,21 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>0.171927447574108</v>
+        <v>8.20151278421798</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0537309909968853</v>
+        <v>2.54715917996006</v>
       </c>
       <c r="F3" t="n">
-        <v>0.958033652073084</v>
+        <v>0.0255991001620332</v>
       </c>
       <c r="G3" t="n">
-        <v>0.976206479905453</v>
+        <v>0.281590101782365</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B4" t="n">
         <v>14</v>
@@ -1533,21 +1389,21 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>-3.20518026774338</v>
+        <v>-0.251835191573122</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.34713424271151</v>
+        <v>-0.102094483504275</v>
       </c>
       <c r="F4" t="n">
-        <v>0.202825390262972</v>
+        <v>0.920367854693366</v>
       </c>
       <c r="G4" t="n">
-        <v>0.558674122720531</v>
+        <v>0.920367854693366</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B5" t="n">
         <v>14</v>
@@ -1556,21 +1412,21 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>10.0267747312995</v>
+        <v>-3.16081921848798</v>
       </c>
       <c r="E5" t="n">
-        <v>2.61134749312012</v>
+        <v>-1.31353976372019</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0227450299789509</v>
+        <v>0.2135612701316</v>
       </c>
       <c r="G5" t="n">
-        <v>0.295685389726361</v>
+        <v>0.599883118160847</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B6" t="n">
         <v>14</v>
@@ -1579,21 +1435,21 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.7666923123686</v>
+        <v>-0.608495751768149</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.210397755776218</v>
+        <v>-0.167058466634683</v>
       </c>
       <c r="F6" t="n">
-        <v>0.836887423425648</v>
+        <v>0.87010613694399</v>
       </c>
       <c r="G6" t="n">
-        <v>0.976206479905453</v>
+        <v>0.920367854693366</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B7" t="n">
         <v>14</v>
@@ -1602,21 +1458,21 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0600667606521319</v>
+        <v>-0.377729081789576</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0304529076003966</v>
+        <v>-0.154014290994612</v>
       </c>
       <c r="F7" t="n">
-        <v>0.976206479905453</v>
+        <v>0.880158308732219</v>
       </c>
       <c r="G7" t="n">
-        <v>0.976206479905453</v>
+        <v>0.920367854693366</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B8" t="n">
         <v>14</v>
@@ -1625,21 +1481,21 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>4.33163642338701</v>
+        <v>2.75416952371274</v>
       </c>
       <c r="E8" t="n">
-        <v>1.40892149151092</v>
+        <v>0.719184433850465</v>
       </c>
       <c r="F8" t="n">
-        <v>0.184240404100712</v>
+        <v>0.485797458944518</v>
       </c>
       <c r="G8" t="n">
-        <v>0.558674122720531</v>
+        <v>0.920367854693366</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B9" t="n">
         <v>14</v>
@@ -1648,21 +1504,21 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>1.44908218717557</v>
+        <v>3.96096534600936</v>
       </c>
       <c r="E9" t="n">
-        <v>0.370687707765383</v>
+        <v>1.55697936897665</v>
       </c>
       <c r="F9" t="n">
-        <v>0.717331002807129</v>
+        <v>0.145444278733568</v>
       </c>
       <c r="G9" t="n">
-        <v>0.976206479905453</v>
+        <v>0.599883118160847</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B10" t="n">
         <v>14</v>
@@ -1671,21 +1527,21 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.8525907371815</v>
+        <v>1.53714101238503</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.15840594538208</v>
+        <v>0.577504423867693</v>
       </c>
       <c r="F10" t="n">
-        <v>0.269233164184488</v>
+        <v>0.574274798396548</v>
       </c>
       <c r="G10" t="n">
-        <v>0.583338522399724</v>
+        <v>0.920367854693366</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B11" t="n">
         <v>14</v>
@@ -1694,21 +1550,21 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>3.21187043743076</v>
+        <v>-0.644705206523761</v>
       </c>
       <c r="E11" t="n">
-        <v>1.89831858288889</v>
+        <v>-0.278404510593708</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0819623580781165</v>
+        <v>0.785441076324928</v>
       </c>
       <c r="G11" t="n">
-        <v>0.532755327507757</v>
+        <v>0.920367854693366</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B12" t="n">
         <v>14</v>
@@ -1717,62 +1573,16 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>1.9749790766767</v>
+        <v>-3.13688370311872</v>
       </c>
       <c r="E12" t="n">
-        <v>0.56513613773166</v>
+        <v>-1.29963202582348</v>
       </c>
       <c r="F12" t="n">
-        <v>0.582392839929746</v>
+        <v>0.218139315694853</v>
       </c>
       <c r="G12" t="n">
-        <v>0.976206479905453</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>23</v>
-      </c>
-      <c r="B13" t="n">
-        <v>14</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" t="n">
-        <v>-0.656868748424042</v>
-      </c>
-      <c r="E13" t="n">
-        <v>-0.283926962392792</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.781305861219183</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.976206479905453</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>23</v>
-      </c>
-      <c r="B14" t="n">
-        <v>14</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" t="n">
-        <v>3.42360773288489</v>
-      </c>
-      <c r="E14" t="n">
-        <v>1.30952519021127</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.21487466258482</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.558674122720531</v>
+        <v>0.599883118160847</v>
       </c>
     </row>
   </sheetData>
@@ -1811,7 +1621,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B2" t="n">
         <v>14</v>
@@ -1820,21 +1630,21 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>-11.2265188179342</v>
+        <v>-32.6238246958074</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.260407576721466</v>
+        <v>-0.46975948140948</v>
       </c>
       <c r="F2" t="n">
-        <v>0.798964075337528</v>
+        <v>0.646948309102902</v>
       </c>
       <c r="G2" t="n">
-        <v>0.798964075337528</v>
+        <v>0.839183026018036</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B3" t="n">
         <v>14</v>
@@ -1843,21 +1653,21 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>39.2681119884081</v>
+        <v>-47.6021236747264</v>
       </c>
       <c r="E3" t="n">
-        <v>0.701999900227956</v>
+        <v>-0.680594570150181</v>
       </c>
       <c r="F3" t="n">
-        <v>0.496070181246581</v>
+        <v>0.509047383813417</v>
       </c>
       <c r="G3" t="n">
-        <v>0.798964075337528</v>
+        <v>0.839183026018036</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B4" t="n">
         <v>14</v>
@@ -1866,21 +1676,21 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>40.5340840271943</v>
+        <v>41.04741387027</v>
       </c>
       <c r="E4" t="n">
-        <v>0.921225815143955</v>
+        <v>0.968395687076343</v>
       </c>
       <c r="F4" t="n">
-        <v>0.375081972603321</v>
+        <v>0.351960315756945</v>
       </c>
       <c r="G4" t="n">
-        <v>0.798964075337528</v>
+        <v>0.839183026018036</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B5" t="n">
         <v>14</v>
@@ -1889,21 +1699,21 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>-42.9080598066367</v>
+        <v>74.6757103088769</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.505639858689371</v>
+        <v>1.84288401325843</v>
       </c>
       <c r="F5" t="n">
-        <v>0.622268791089178</v>
+        <v>0.0901747870524845</v>
       </c>
       <c r="G5" t="n">
-        <v>0.798964075337528</v>
+        <v>0.839183026018036</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B6" t="n">
         <v>14</v>
@@ -1912,21 +1722,21 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>-26.7382298362105</v>
+        <v>-13.4640007596346</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.413577309568212</v>
+        <v>-0.207390012122588</v>
       </c>
       <c r="F6" t="n">
-        <v>0.686479039072496</v>
+        <v>0.839183026018036</v>
       </c>
       <c r="G6" t="n">
-        <v>0.798964075337528</v>
+        <v>0.839183026018036</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B7" t="n">
         <v>14</v>
@@ -1935,21 +1745,21 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>11.4448052139025</v>
+        <v>-11.2825481554086</v>
       </c>
       <c r="E7" t="n">
-        <v>0.326768459489144</v>
+        <v>-0.258400999532546</v>
       </c>
       <c r="F7" t="n">
-        <v>0.749472163189408</v>
+        <v>0.800476149296803</v>
       </c>
       <c r="G7" t="n">
-        <v>0.798964075337528</v>
+        <v>0.839183026018036</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B8" t="n">
         <v>14</v>
@@ -1958,21 +1768,21 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>47.5385092307838</v>
+        <v>34.1569235512862</v>
       </c>
       <c r="E8" t="n">
-        <v>0.825592142940171</v>
+        <v>0.494627084609257</v>
       </c>
       <c r="F8" t="n">
-        <v>0.425144845411032</v>
+        <v>0.629794727110232</v>
       </c>
       <c r="G8" t="n">
-        <v>0.798964075337528</v>
+        <v>0.839183026018036</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B9" t="n">
         <v>14</v>
@@ -1981,21 +1791,21 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>30.0569363822183</v>
+        <v>13.1741924888915</v>
       </c>
       <c r="E9" t="n">
-        <v>0.431984979690657</v>
+        <v>0.265615880246634</v>
       </c>
       <c r="F9" t="n">
-        <v>0.673412570506239</v>
+        <v>0.795043297729328</v>
       </c>
       <c r="G9" t="n">
-        <v>0.798964075337528</v>
+        <v>0.839183026018036</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B10" t="n">
         <v>14</v>
@@ -2004,21 +1814,21 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>75.7807727746869</v>
+        <v>35.1482371921958</v>
       </c>
       <c r="E10" t="n">
-        <v>1.85662716593615</v>
+        <v>0.747129380725264</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0880718160690156</v>
+        <v>0.469372535062918</v>
       </c>
       <c r="G10" t="n">
-        <v>0.798964075337528</v>
+        <v>0.839183026018036</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B11" t="n">
         <v>14</v>
@@ -2027,21 +1837,21 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>-41.6541843226561</v>
+        <v>-43.0118212153558</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.29199142333502</v>
+        <v>-1.08809637483211</v>
       </c>
       <c r="F11" t="n">
-        <v>0.220688078984999</v>
+        <v>0.297923740660909</v>
       </c>
       <c r="G11" t="n">
-        <v>0.798964075337528</v>
+        <v>0.839183026018036</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B12" t="n">
         <v>14</v>
@@ -2050,62 +1860,16 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>-53.019619202381</v>
+        <v>41.1315171469441</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.865363652821161</v>
+        <v>0.926016752579146</v>
       </c>
       <c r="F12" t="n">
-        <v>0.403808060835194</v>
+        <v>0.37268614705574</v>
       </c>
       <c r="G12" t="n">
-        <v>0.798964075337528</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>24</v>
-      </c>
-      <c r="B13" t="n">
-        <v>14</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" t="n">
-        <v>-42.5757501769059</v>
-      </c>
-      <c r="E13" t="n">
-        <v>-1.0769651745174</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.302670689320869</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.798964075337528</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>24</v>
-      </c>
-      <c r="B14" t="n">
-        <v>14</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" t="n">
-        <v>18.0327259733558</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0.363745533122724</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.722375899486181</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.798964075337528</v>
+        <v>0.839183026018036</v>
       </c>
     </row>
   </sheetData>
@@ -2144,7 +1908,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B2" t="n">
         <v>13</v>
@@ -2153,21 +1917,21 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>-6.10399175482253</v>
+        <v>-18.4573920882855</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.799650613365431</v>
+        <v>-1.36206891271826</v>
       </c>
       <c r="F2" t="n">
-        <v>0.44083981690418</v>
+        <v>0.200416458163333</v>
       </c>
       <c r="G2" t="n">
-        <v>0.717842228328179</v>
+        <v>0.634295886692396</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B3" t="n">
         <v>13</v>
@@ -2176,21 +1940,21 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>-15.9581637520481</v>
+        <v>10.2346965923448</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.34923232015578</v>
+        <v>0.81509490412756</v>
       </c>
       <c r="F3" t="n">
-        <v>0.204378787269934</v>
+        <v>0.432312020375935</v>
       </c>
       <c r="G3" t="n">
-        <v>0.714486844480562</v>
+        <v>0.679347460590756</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B4" t="n">
         <v>13</v>
@@ -2199,21 +1963,21 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>-5.09908659216794</v>
+        <v>-11.2765796015314</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.628784829341415</v>
+        <v>-1.26894832755631</v>
       </c>
       <c r="F4" t="n">
-        <v>0.542326483546246</v>
+        <v>0.230653049706326</v>
       </c>
       <c r="G4" t="n">
-        <v>0.727872516272511</v>
+        <v>0.634295886692396</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B5" t="n">
         <v>13</v>
@@ -2222,21 +1986,21 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>15.2780556135333</v>
+        <v>-1.80306351027098</v>
       </c>
       <c r="E5" t="n">
-        <v>1.02866542816105</v>
+        <v>-0.211820614338119</v>
       </c>
       <c r="F5" t="n">
-        <v>0.325725401211196</v>
+        <v>0.836120603506072</v>
       </c>
       <c r="G5" t="n">
-        <v>0.717842228328179</v>
+        <v>0.836120603506072</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B6" t="n">
         <v>13</v>
@@ -2245,21 +2009,21 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>9.18454318341849</v>
+        <v>9.55869811208761</v>
       </c>
       <c r="E6" t="n">
-        <v>0.801080835343435</v>
+        <v>0.835056139092426</v>
       </c>
       <c r="F6" t="n">
-        <v>0.440045499932631</v>
+        <v>0.421452739601316</v>
       </c>
       <c r="G6" t="n">
-        <v>0.717842228328179</v>
+        <v>0.679347460590756</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B7" t="n">
         <v>13</v>
@@ -2268,21 +2032,21 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>-12.474684326687</v>
+        <v>-6.37057743580847</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.27579404724604</v>
+        <v>-0.826177676887135</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0438590164556356</v>
+        <v>0.426260098844207</v>
       </c>
       <c r="G7" t="n">
-        <v>0.570167213923263</v>
+        <v>0.679347460590756</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B8" t="n">
         <v>13</v>
@@ -2291,21 +2055,21 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>-7.01211867705781</v>
+        <v>2.91048401084958</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.601184280111743</v>
+        <v>0.228426177223102</v>
       </c>
       <c r="F8" t="n">
-        <v>0.559901935594239</v>
+        <v>0.823505852634669</v>
       </c>
       <c r="G8" t="n">
-        <v>0.727872516272511</v>
+        <v>0.836120603506072</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B9" t="n">
         <v>13</v>
@@ -2314,21 +2078,21 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>2.6093524890737</v>
+        <v>-4.96764544897997</v>
       </c>
       <c r="E9" t="n">
-        <v>0.199858965835121</v>
+        <v>-0.516210760937391</v>
       </c>
       <c r="F9" t="n">
-        <v>0.84523764446765</v>
+        <v>0.61592521819008</v>
       </c>
       <c r="G9" t="n">
-        <v>0.900736299669055</v>
+        <v>0.752797488898987</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B10" t="n">
         <v>13</v>
@@ -2337,21 +2101,21 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.09317811605223</v>
+        <v>-17.5282697651802</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.127641428888451</v>
+        <v>-1.93468673266174</v>
       </c>
       <c r="F10" t="n">
-        <v>0.900736299669055</v>
+        <v>0.0791534935642685</v>
       </c>
       <c r="G10" t="n">
-        <v>0.900736299669055</v>
+        <v>0.55086260419686</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B11" t="n">
         <v>13</v>
@@ -2360,21 +2124,21 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>4.83069851155722</v>
+        <v>13.442575691753</v>
       </c>
       <c r="E11" t="n">
-        <v>0.798015519800457</v>
+        <v>1.79494498483688</v>
       </c>
       <c r="F11" t="n">
-        <v>0.441749063586572</v>
+        <v>0.100156837126702</v>
       </c>
       <c r="G11" t="n">
-        <v>0.717842228328179</v>
+        <v>0.55086260419686</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B12" t="n">
         <v>13</v>
@@ -2383,62 +2147,16 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>4.169190623636</v>
+        <v>-4.68419259608894</v>
       </c>
       <c r="E12" t="n">
-        <v>0.353959800483271</v>
+        <v>-0.571192175375095</v>
       </c>
       <c r="F12" t="n">
-        <v>0.730060393144152</v>
+        <v>0.579352270722855</v>
       </c>
       <c r="G12" t="n">
-        <v>0.862798646443089</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>25</v>
-      </c>
-      <c r="B13" t="n">
-        <v>13</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" t="n">
-        <v>13.2610731040019</v>
-      </c>
-      <c r="E13" t="n">
-        <v>1.76894294484622</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.104585481755578</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.679805631411257</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>25</v>
-      </c>
-      <c r="B14" t="n">
-        <v>13</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" t="n">
-        <v>-12.7688244403981</v>
-      </c>
-      <c r="E14" t="n">
-        <v>-1.30102566290924</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.219842105994019</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.714486844480562</v>
+        <v>0.752797488898987</v>
       </c>
     </row>
   </sheetData>
@@ -2454,45 +2172,45 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" t="s">
         <v>26</v>
-      </c>
-      <c r="B1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" t="s">
-        <v>28</v>
       </c>
       <c r="D1" t="s">
         <v>0</v>
       </c>
       <c r="E1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G1" t="s">
         <v>29</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>30</v>
-      </c>
-      <c r="G1" t="s">
-        <v>31</v>
-      </c>
-      <c r="H1" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" t="s">
         <v>33</v>
-      </c>
-      <c r="B2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C2" t="s">
-        <v>35</v>
       </c>
       <c r="D2" t="s">
         <v>7</v>
       </c>
       <c r="E2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -2501,50 +2219,50 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>4.62351749580375</v>
+        <v>5.44004819871796</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" t="s">
         <v>33</v>
       </c>
-      <c r="B3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C3" t="s">
-        <v>35</v>
-      </c>
       <c r="D3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E3" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>7.01211867705781</v>
+        <v>9.55869811208761</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" t="s">
         <v>33</v>
       </c>
-      <c r="B4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C4" t="s">
-        <v>35</v>
-      </c>
       <c r="D4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -2553,50 +2271,50 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>40.5340840271943</v>
+        <v>35.1482371921958</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" t="s">
         <v>33</v>
       </c>
-      <c r="B5" t="s">
-        <v>34</v>
-      </c>
-      <c r="C5" t="s">
-        <v>35</v>
-      </c>
       <c r="D5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E5" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>1494.46784401706</v>
+        <v>1019.06929145149</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" t="s">
         <v>33</v>
       </c>
-      <c r="B6" t="s">
-        <v>34</v>
-      </c>
-      <c r="C6" t="s">
-        <v>35</v>
-      </c>
       <c r="D6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E6" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -2605,24 +2323,24 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>1388.78967438055</v>
+        <v>815.492404145446</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" t="s">
         <v>33</v>
       </c>
-      <c r="B7" t="s">
-        <v>34</v>
-      </c>
-      <c r="C7" t="s">
-        <v>35</v>
-      </c>
       <c r="D7" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E7" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F7" t="n">
         <v>1</v>
@@ -2631,7 +2349,7 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>1.9749790766767</v>
+        <v>1.53714101238503</v>
       </c>
     </row>
   </sheetData>
